--- a/QCM4_3_PHY.xlsx
+++ b/QCM4_3_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FA1159-C966-4EE9-A773-0AD26E1E385D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775302A6-2D30-460E-B786-76EFC103318D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="125">
   <si>
     <t>Question</t>
   </si>
@@ -379,20 +379,31 @@
   </si>
   <si>
     <t>Le mouvement : Le wagon de queue d'un train se détache alors qu'il aborde une côte à la vitesse $v_0 = 30\text{ m.s}^{-1}$. La masse du wagon et des voyageurs est de $170\text{ tonnes}$, la voie fait un angle de $10^\circ$ avec l'horizontale. Les roues du wagon sont freinées par un frottement solide d'intensité constante $F = 221\text{ kN}$. Une fois immobilisé, le wagon redescend. 
-&lt;img src="/images/PHY_QCM1_4_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 Données : $\sin(10^\circ)=0,17 \Rightarrow g\sin(10^\circ)=1,7\text{ m.s}^{-2}$; $17^2=289$; $4\times 17 = 68$; $51/17=3$ ; $221/170=1,3$ ; $170/221=0,77$. Le frottement solide est présent lors de la montée et de la descente avec la même intensité.</t>
   </si>
   <si>
-    <t>La bille : La bille ponctuelle M est lancée vers le haut. $\vec{v}_0 = -6 \vec{i}$ ; $x_0 = 5,0\text{ m}$ ; $\vec{a} = 2\vec{i}$.
-&lt;img src="/images/PHY_QCM1_4_Q4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
-    <t>Un rail rectiligne : Un solide S de masse $100\text{ g}$ sur un rail rectiligne de longueur $AB= 1\text{ m}$ et incliné d'un angle $\alpha= 30^\circ$ par rapport au plan horizontal. À $t = 0$ le solide est lancé sur le rail du point A avec une vitesse initiale $v_0$. Le graphe représente la variation de la vitesse $v$ du solide lors de son mouvement en fonction du temps ($g = 10\text{ m.s}^{-2}$).
-&lt;img src="/images/PHY_QCM1_4_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
-    <t>Un quart de cercle : Un mobile S quasi ponctuel, de masse $m = 500\text{ g}$, glisse sur une piste AB située dans un plan vertical. Il a été lâché d'un point M sans vitesse initiale. La partie AB est un quart de cercle de rayon $R = 20\text{ cm}$. Les frottements sont négligeables. On prendra $g = 10\text{ m.s}^{-2}$.
-&lt;img src="/images/PHY_QCM1_4_Q6.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+    <t xml:space="preserve">La bille : La bille ponctuelle M est lancée vers le haut. $\vec{v}_0 = -6 \vec{i}$ ; $x_0 = 5,0\text{ m}$ ; $\vec{a} = 2\vec{i}$.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un rail rectiligne : Un solide S de masse $100\text{ g}$ sur un rail rectiligne de longueur $AB= 1\text{ m}$ et incliné d'un angle $\alpha= 30^\circ$ par rapport au plan horizontal. À $t = 0$ le solide est lancé sur le rail du point A avec une vitesse initiale $v_0$. Le graphe représente la variation de la vitesse $v$ du solide lors de son mouvement en fonction du temps ($g = 10\text{ m.s}^{-2}$).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un quart de cercle : Un mobile S quasi ponctuel, de masse $m = 500\text{ g}$, glisse sur une piste AB située dans un plan vertical. Il a été lâché d'un point M sans vitesse initiale. La partie AB est un quart de cercle de rayon $R = 20\text{ cm}$. Les frottements sont négligeables. On prendra $g = 10\text{ m.s}^{-2}$.
+</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q3.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q4.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q5.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q6.png</t>
   </si>
 </sst>
 </file>
@@ -904,7 +915,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="204" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>117</v>
       </c>
@@ -931,6 +942,9 @@
       </c>
       <c r="I2" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1011,7 +1025,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>118</v>
       </c>
@@ -1038,6 +1052,9 @@
       </c>
       <c r="I6" s="9" t="s">
         <v>34</v>
+      </c>
+      <c r="J6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -1231,7 +1248,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>119</v>
       </c>
@@ -1258,6 +1275,9 @@
       </c>
       <c r="I14" s="10" t="s">
         <v>73</v>
+      </c>
+      <c r="J14" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -1312,7 +1332,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
         <v>111</v>
       </c>
@@ -1336,7 +1356,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>112</v>
       </c>
@@ -1362,7 +1382,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="102" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>120</v>
       </c>
@@ -1388,8 +1408,11 @@
       <c r="I19" s="7" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="J19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
         <v>114</v>
       </c>
@@ -1415,7 +1438,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
         <v>115</v>
       </c>
@@ -1441,7 +1464,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>116</v>
       </c>

--- a/QCM4_3_PHY.xlsx
+++ b/QCM4_3_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775302A6-2D30-460E-B786-76EFC103318D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102833C4-3F73-4B84-B53C-D9E05AD50453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="127">
   <si>
     <t>Question</t>
   </si>
@@ -87,9 +87,6 @@
     <t>$\text{kg.m}^1\text{.s}^{-2}$</t>
   </si>
   <si>
-    <t>$\text{kg.m}^{-1}\text{.s}^{-2}$</t>
-  </si>
-  <si>
     <t>$\text{kg.m}^1\text{.s}^2$</t>
   </si>
   <si>
@@ -123,9 +120,6 @@
     <t>$0,4\text{ m.s}^{-2}$</t>
   </si>
   <si>
-    <t>$1\text{ m.s}^{-2}$</t>
-  </si>
-  <si>
     <t>$0\text{ m.s}^{-2}$</t>
   </si>
   <si>
@@ -144,9 +138,6 @@
     <t>Autre.</t>
   </si>
   <si>
-    <t>La bille (Suite) : $\vec{v}_0 = -6 \vec{i}$ ; $x_0 = 5,0\text{ m}$ ; $\vec{a} = 2\vec{i}$.</t>
-  </si>
-  <si>
     <t>$x(t)=t^2+6t+5$</t>
   </si>
   <si>
@@ -159,9 +150,6 @@
     <t>$x(t)=t^2+3t+5$</t>
   </si>
   <si>
-    <t>$x(t)=-t^2-6t+1$</t>
-  </si>
-  <si>
     <t>$0\text{ m.s}^{-1}$</t>
   </si>
   <si>
@@ -177,9 +165,6 @@
     <t>$4\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t>Un projectile ponctuel : Un projectile ponctuel de masse $m=50,0\text{ g}$ est lancé depuis le sol, verticalement, avec une vitesse initiale $v_0$. Il s'élève de $10\text{ m}$ avant de redescendre. On néglige tous les frottements.</t>
-  </si>
-  <si>
     <t>$3,5\text{ m.s}^{-1}$</t>
   </si>
   <si>
@@ -189,12 +174,6 @@
     <t>$14\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t>L'angle de tir est maintenant compris entre $0$ et $90^\circ$. On prendra $v_0 = 10\text{ m.s}^{-1}$.</t>
-  </si>
-  <si>
-    <t>$E_{pe}$</t>
-  </si>
-  <si>
     <t>$E_c$</t>
   </si>
   <si>
@@ -204,9 +183,6 @@
     <t>$E_{pe}$ (élastique)</t>
   </si>
   <si>
-    <t>$2,5\text{ m}$</t>
-  </si>
-  <si>
     <t>$5\text{ m}$</t>
   </si>
   <si>
@@ -246,9 +222,6 @@
     <t>$a_G = 0,2\text{ m.s}^{-2}$</t>
   </si>
   <si>
-    <t>À déterminer (graphique)</t>
-  </si>
-  <si>
     <t>$v_B = 1,14\text{ m.s}^{-1}$</t>
   </si>
   <si>
@@ -261,9 +234,6 @@
     <t>$v_B = 4,11\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t>$t_B = 0,63\text{ s}$</t>
-  </si>
-  <si>
     <t>$t_B = 0,83\text{ s}$</t>
   </si>
   <si>
@@ -297,21 +267,12 @@
     <t>$W = -0,55\text{ J}$</t>
   </si>
   <si>
-    <t>À déterminer</t>
-  </si>
-  <si>
     <t>$E_m = cte$</t>
   </si>
   <si>
     <t>$E_m = 0$</t>
   </si>
   <si>
-    <t>$E_c = \frac{1}{2} m \theta$</t>
-  </si>
-  <si>
-    <t>$E_c = \frac{1}{2} m R \theta^2$</t>
-  </si>
-  <si>
     <t>$E_c = \frac{1}{2} m v^2$</t>
   </si>
   <si>
@@ -342,15 +303,6 @@
     <t>La vitesse $v_0$ est :</t>
   </si>
   <si>
-    <t>Au point le plus haut de la trajectoire, l'énergie mécanique du projectile est uniquement sous forme :</t>
-  </si>
-  <si>
-    <t>La portée est :</t>
-  </si>
-  <si>
-    <t>À l'abscisse égale à la portée du tir de $10\text{ m}$, l'énergie cinétique du projectile vaut :</t>
-  </si>
-  <si>
     <t>L'accélération $a_G$ du centre d'inertie du solide est :</t>
   </si>
   <si>
@@ -378,32 +330,92 @@
     <t>La vitesse du mobile au point B est de :</t>
   </si>
   <si>
-    <t>Le mouvement : Le wagon de queue d'un train se détache alors qu'il aborde une côte à la vitesse $v_0 = 30\text{ m.s}^{-1}$. La masse du wagon et des voyageurs est de $170\text{ tonnes}$, la voie fait un angle de $10^\circ$ avec l'horizontale. Les roues du wagon sont freinées par un frottement solide d'intensité constante $F = 221\text{ kN}$. Une fois immobilisé, le wagon redescend. 
-Données : $\sin(10^\circ)=0,17 \Rightarrow g\sin(10^\circ)=1,7\text{ m.s}^{-2}$; $17^2=289$; $4\times 17 = 68$; $51/17=3$ ; $221/170=1,3$ ; $170/221=0,77$. Le frottement solide est présent lors de la montée et de la descente avec la même intensité.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La bille : La bille ponctuelle M est lancée vers le haut. $\vec{v}_0 = -6 \vec{i}$ ; $x_0 = 5,0\text{ m}$ ; $\vec{a} = 2\vec{i}$.
+    <t>PHY_QCM1_4_Q3.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q4.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q5.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q6.png</t>
+  </si>
+  <si>
+    <t>$\text{kg.m}^{-1}\text{.s}^{2}$</t>
+  </si>
+  <si>
+    <t>$-0,3\text{ m.s}^{-2}$</t>
+  </si>
+  <si>
+    <t>$-3\text{ m.s}^{-2}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Le mouvement : &lt;/b&gt;&lt;/center&gt;
+Le wagon de queue d'un train se détache alors qu'il aborde une côte à la vitesse $v_0 = 30\text{ m.s}^{-1}$. La masse du wagon et des voyageurs est de $170\text{ tonnes}$, la voie fait un angle de $10^\circ$ avec l'horizontale. Les roues du wagon sont freinées par un frottement solide d'intensité constante $F = 221\text{ kN}$. Une fois immobilisé, le wagon redescend. 
+&lt;br&gt;Données : $\sin(10^\circ)=0,17 \Rightarrow g\sin(10^\circ)=1,7\text{ m.s}^{-2}$; $17^2=289$; $4\times 17 = 68$; $51/17=3$ ; $221/170=1,3$ ; $170/221=0,77$. Le frottement solide est présent lors de la montée et de la descente avec la même intensité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;La bille : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;La bille ponctuelle M est lancée vers le haut. $\vec{v}_0 = -6 \vec{i}$ ; $x_0 = 5,0\text{ m}$ ; $\vec{a} = 2\vec{i}$.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Un rail rectiligne : Un solide S de masse $100\text{ g}$ sur un rail rectiligne de longueur $AB= 1\text{ m}$ et incliné d'un angle $\alpha= 30^\circ$ par rapport au plan horizontal. À $t = 0$ le solide est lancé sur le rail du point A avec une vitesse initiale $v_0$. Le graphe représente la variation de la vitesse $v$ du solide lors de son mouvement en fonction du temps ($g = 10\text{ m.s}^{-2}$).
+    <t>$x(t)=-t^2-6t+5$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Un projectile ponctuel : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Un projectile ponctuel de masse $m=50,0\text{ g}$ est lancé depuis le sol, verticalement, avec une vitesse initiale $v_0$. Il s'élève de $10\text{ m}$ avant de redescendre. On néglige tous les frottements.</t>
+  </si>
+  <si>
+    <t>L'angle de tir est maintenant compris entre $0$ et $90^\circ$. On prendra $v_0 = 10\text{ m.s}^{-1}$ au point le plus haut de la trajectoire.
+L'énergie mécanique du projectile est uniquement sous forme :</t>
+  </si>
+  <si>
+    <t>$E_{pp}$</t>
+  </si>
+  <si>
+    <t>Pour $\alpha = 45°$, la portée est :</t>
+  </si>
+  <si>
+    <t>$0\text{ m}$</t>
+  </si>
+  <si>
+    <t>Au point d'abscisse égal à la portée du tir de $10\text{ m}$, l'énergie cinétique du projectile vaut :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Un rail rectiligne : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Un solide S de masse $100\text{ g}$ sur un rail rectiligne de longueur $AB= 1\text{ m}$ et incliné d'un angle $\alpha= 30^\circ$ par rapport au plan horizontal. À $t = 0$ le solide est lancé sur le rail du point A avec une vitesse initiale $v_0$. Le graphe représente la variation de la vitesse $v$ du solide lors de son mouvement en fonction du temps ($g = 10\text{ m.s}^{-2}$).
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Un quart de cercle : Un mobile S quasi ponctuel, de masse $m = 500\text{ g}$, glisse sur une piste AB située dans un plan vertical. Il a été lâché d'un point M sans vitesse initiale. La partie AB est un quart de cercle de rayon $R = 20\text{ cm}$. Les frottements sont négligeables. On prendra $g = 10\text{ m.s}^{-2}$.
+    <t>$t_B = 0,61\text{ s}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Un quart de cercle : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Un mobile S quasi ponctuel, de masse $m = 500\text{ g}$, glisse sur une piste AB située dans un plan vertical. Il a été lâché d'un point A sans vitesse initiale. La partie AB est un quart de cercle de rayon $R = 20\text{ cm}$. Les frottements sont négligeables. On prendra $g = 10\text{ m.s}^{-2}$.
 </t>
   </si>
   <si>
-    <t>PHY_QCM1_4_Q3.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_4_Q4.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_4_Q5.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_4_Q6.png</t>
+    <t>$E_m \neq cte$</t>
+  </si>
+  <si>
+    <t>$E_m \neq 0$</t>
+  </si>
+  <si>
+    <t>$E_c = \frac{1}{2} m \theta^{2}$</t>
+  </si>
+  <si>
+    <t>$E_c = \frac{1}{2} m R^2 \dot{\theta}^2$</t>
+  </si>
+  <si>
+    <t>$E_c = \frac{1}{2} m \dot{\theta}^2$</t>
+  </si>
+  <si>
+    <t>$E_c = \frac{1}{2} m \dot{\theta}$</t>
+  </si>
+  <si>
+    <t>$E_c = \frac{1}{2} m v$</t>
   </si>
 </sst>
 </file>
@@ -915,12 +927,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
@@ -932,50 +944,50 @@
         <v>19</v>
       </c>
       <c r="F2" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>27</v>
-      </c>
       <c r="I3" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
@@ -990,7 +1002,7 @@
         <v>17</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>14</v>
@@ -1001,493 +1013,475 @@
     </row>
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="G5" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="I6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>49</v>
-      </c>
       <c r="I8" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="I9" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
       <c r="J14" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>73</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+    </row>
+    <row r="19" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="E19" s="7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G19" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J19" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>49</v>
-      </c>
       <c r="I22" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/QCM4_3_PHY.xlsx
+++ b/QCM4_3_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102833C4-3F73-4B84-B53C-D9E05AD50453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53458FA3-77B0-4B55-9C6A-46EF077623A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="125">
   <si>
     <t>Question</t>
   </si>
@@ -117,9 +117,6 @@
     <t>$0,3\text{ m.s}^{-2}$</t>
   </si>
   <si>
-    <t>$0,4\text{ m.s}^{-2}$</t>
-  </si>
-  <si>
     <t>$0\text{ m.s}^{-2}$</t>
   </si>
   <si>
@@ -271,9 +268,6 @@
   </si>
   <si>
     <t>$E_m = 0$</t>
-  </si>
-  <si>
-    <t>$E_c = \frac{1}{2} m v^2$</t>
   </si>
   <si>
     <t>L'unité du Newton est :</t>
@@ -929,10 +923,10 @@
     </row>
     <row r="2" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
@@ -944,7 +938,7 @@
         <v>19</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>20</v>
@@ -956,12 +950,12 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
@@ -987,7 +981,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
@@ -1013,7 +1007,7 @@
     </row>
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
@@ -1022,466 +1016,474 @@
         <v>28</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="I6" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>45</v>
-      </c>
       <c r="I8" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="I9" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>55</v>
-      </c>
       <c r="I12" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="I13" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="I14" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="J14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>68</v>
-      </c>
       <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
+      <c r="I15" s="9" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+      <c r="I16" s="7" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
+      <c r="I18" s="7" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="19" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>121</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>13</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="G20" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="H20" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>126</v>
-      </c>
       <c r="I20" s="9" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="G21" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="H21" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="I21" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="G22" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="H22" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H22" s="9" t="s">
-        <v>45</v>
-      </c>
       <c r="I22" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
